--- a/data/trans_orig/Q02D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_R-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas diarias, a la semana, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan</t>
+          <t>Número medio de horas diarias, a la semana, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,57 +721,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 4,82</t>
+          <t>3,82; 4,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,92</t>
+          <t>5,12; 6,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 11,02</t>
+          <t>6,0; 11,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,21</t>
+          <t>4,51; 6,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 6,99</t>
+          <t>5,82; 7,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,32; 10,29</t>
+          <t>8,29; 10,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 9,4</t>
+          <t>6,79; 9,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 4,75</t>
+          <t>3,73; 4,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 5,83</t>
+          <t>5,0; 5,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 8,64</t>
+          <t>7,23; 8,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 9,35</t>
+          <t>6,82; 9,45</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,48</t>
+          <t>2,88; 4,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,44</t>
+          <t>4,2; 5,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,13; 7,92</t>
+          <t>6,04; 7,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,44</t>
+          <t>3,29; 5,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 7,3</t>
+          <t>5,44; 7,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 7,57</t>
+          <t>6,41; 7,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 10,61</t>
+          <t>8,64; 10,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 12,37</t>
+          <t>7,12; 11,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 5,89</t>
+          <t>4,71; 5,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 6,47</t>
+          <t>5,55; 6,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 9,14</t>
+          <t>7,79; 9,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,93; 9,66</t>
+          <t>5,87; 9,44</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,74</t>
+          <t>3,14; 4,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 5,85</t>
+          <t>4,8; 5,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 8,36</t>
+          <t>6,22; 8,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 11,05</t>
+          <t>5,2; 11,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 6,59</t>
+          <t>4,39; 6,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 6,71</t>
+          <t>5,45; 6,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,38</t>
+          <t>6,26; 9,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 14,99</t>
+          <t>7,49; 15,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 5,08</t>
+          <t>3,8; 4,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 5,98</t>
+          <t>5,14; 6,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,29</t>
+          <t>6,52; 8,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,84</t>
+          <t>6,21; 11,16</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 4,86</t>
+          <t>3,7; 4,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 5,35</t>
+          <t>4,6; 5,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,69; 8,25</t>
+          <t>6,66; 8,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 7,41</t>
+          <t>4,99; 7,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 7,22</t>
+          <t>5,68; 7,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 7,32</t>
+          <t>6,52; 7,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,82; 10,28</t>
+          <t>8,81; 10,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,0; 10,33</t>
+          <t>7,87; 10,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,86</t>
+          <t>4,89; 5,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 6,29</t>
+          <t>5,72; 6,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 9,16</t>
+          <t>8,09; 9,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 8,54</t>
+          <t>6,82; 8,56</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,08</t>
+          <t>3,79; 7,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,97</t>
+          <t>4,72; 6,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 7,89</t>
+          <t>5,83; 8,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,88; 10,02</t>
+          <t>4,74; 9,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,82</t>
+          <t>6,12; 7,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 7,28</t>
+          <t>6,39; 7,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,95</t>
+          <t>7,42; 9,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,91; 8,61</t>
+          <t>6,91; 8,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,72; 7,22</t>
+          <t>5,66; 7,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 6,8</t>
+          <t>6,04; 6,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,04; 8,28</t>
+          <t>7,05; 8,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 8,38</t>
+          <t>6,71; 8,33</t>
         </is>
       </c>
     </row>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 9,25</t>
+          <t>2,42; 9,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,67</t>
+          <t>1,59; 3,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,72</t>
+          <t>2,88; 5,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,44; 6,99</t>
+          <t>5,46; 6,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,31; 7,29</t>
+          <t>6,33; 7,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,9; 9,81</t>
+          <t>7,75; 9,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,13</t>
+          <t>5,1; 8,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,46; 6,88</t>
+          <t>5,4; 6,87</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,18; 7,18</t>
+          <t>6,16; 7,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,34</t>
+          <t>7,52; 9,38</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,66</t>
+          <t>4,68; 7,86</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,63; 4,33</t>
+          <t>3,65; 4,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 5,16</t>
+          <t>4,68; 5,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,5; 7,34</t>
+          <t>6,49; 7,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,29</t>
+          <t>5,5; 7,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 6,56</t>
+          <t>5,89; 6,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 6,98</t>
+          <t>6,54; 6,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,55; 9,34</t>
+          <t>8,53; 9,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,44; 8,71</t>
+          <t>7,44; 8,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,1; 5,62</t>
+          <t>5,09; 5,62</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,87; 6,2</t>
+          <t>5,87; 6,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,84; 8,39</t>
+          <t>7,86; 8,44</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,96</t>
+          <t>6,89; 7,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q02D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_R-Clase-trans_orig.xlsx
@@ -663,47 +663,47 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>7,54</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,27</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,41</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,26</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7,65</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4,22</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5,39</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>7,91</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,27</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,41</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,26</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7,84</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4,22</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5,39</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7,91</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,87</t>
+          <t>7,6</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 3,92</t>
+          <t>2,81; 3,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 4,76</t>
+          <t>3,81; 4,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 6,91</t>
+          <t>5,11; 6,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 11,09</t>
+          <t>5,78; 10,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,21</t>
+          <t>4,48; 6,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,06</t>
+          <t>5,77; 7,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 10,4</t>
+          <t>8,26; 10,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 9,45</t>
+          <t>6,7; 9,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 4,77</t>
+          <t>3,78; 4,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 5,82</t>
+          <t>4,99; 5,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 8,72</t>
+          <t>7,24; 8,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 9,45</t>
+          <t>6,65; 9,1</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>4,25</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,13</t>
+          <t>8,89</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,3</t>
+          <t>7,09</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,44</t>
+          <t>2,86; 4,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,41</t>
+          <t>4,25; 5,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 7,82</t>
+          <t>6,15; 7,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,56</t>
+          <t>3,37; 5,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,13</t>
+          <t>5,52; 7,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 7,55</t>
+          <t>6,35; 7,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 10,5</t>
+          <t>8,61; 10,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 11,99</t>
+          <t>7,22; 11,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,71; 5,99</t>
+          <t>4,64; 5,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 6,44</t>
+          <t>5,57; 6,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 9,16</t>
+          <t>7,82; 9,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,44</t>
+          <t>5,74; 9,41</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>6,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,56</t>
+          <t>10,16</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>7,57</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,63</t>
+          <t>3,14; 4,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 5,86</t>
+          <t>4,77; 5,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,29</t>
+          <t>6,31; 8,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 11,01</t>
+          <t>4,92; 10,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,6</t>
+          <t>4,26; 6,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 6,82</t>
+          <t>5,37; 6,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 9,45</t>
+          <t>6,37; 9,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 15,03</t>
+          <t>7,04; 14,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 4,95</t>
+          <t>3,7; 4,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,0</t>
+          <t>5,21; 6,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,23</t>
+          <t>6,52; 8,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,16</t>
+          <t>5,91; 10,45</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>6,29</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,97</t>
+          <t>8,99</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,6</t>
+          <t>7,68</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 4,9</t>
+          <t>3,67; 4,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 5,38</t>
+          <t>4,57; 5,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 8,2</t>
+          <t>6,73; 8,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,42</t>
+          <t>5,36; 7,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 7,19</t>
+          <t>5,64; 7,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 7,35</t>
+          <t>6,5; 7,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,81; 10,27</t>
+          <t>8,78; 10,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 10,26</t>
+          <t>7,97; 10,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 5,88</t>
+          <t>4,91; 5,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 6,28</t>
+          <t>5,72; 6,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 9,15</t>
+          <t>8,1; 9,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,56</t>
+          <t>6,92; 8,58</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,63</t>
+          <t>7,64</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,43</t>
+          <t>7,33</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,13</t>
+          <t>3,84; 7,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 6,03</t>
+          <t>4,72; 6,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,15</t>
+          <t>5,78; 8,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,76</t>
+          <t>4,7; 8,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 7,88</t>
+          <t>6,06; 7,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 7,3</t>
+          <t>6,36; 7,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,05</t>
+          <t>7,3; 8,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,91; 8,71</t>
+          <t>6,98; 8,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 7,17</t>
+          <t>5,68; 7,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 6,8</t>
+          <t>6,03; 6,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 8,35</t>
+          <t>7,0; 8,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,33</t>
+          <t>6,66; 8,11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,93</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,22</t>
+          <t>6,48</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,8</t>
+          <t>5,99</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,66</t>
+          <t>2,3; 9,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,68</t>
+          <t>1,59; 3,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,75</t>
+          <t>3,0; 6,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 8,29</t>
+          <t>2,04; 7,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,46; 6,95</t>
+          <t>5,46; 6,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 7,3</t>
+          <t>6,3; 7,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,75; 9,76</t>
+          <t>7,81; 9,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,1; 8,45</t>
+          <t>5,24; 8,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,4; 6,87</t>
+          <t>5,46; 6,94</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,16; 7,15</t>
+          <t>6,19; 7,19</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,52; 9,38</t>
+          <t>7,52; 9,31</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,86</t>
+          <t>4,84; 7,62</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,99</t>
+          <t>7,95</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,35</t>
+          <t>7,27</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,65; 4,34</t>
+          <t>3,65; 4,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,13</t>
+          <t>4,69; 5,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,49; 7,32</t>
+          <t>6,46; 7,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 7,39</t>
+          <t>5,42; 7,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 6,59</t>
+          <t>5,89; 6,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,54; 6,95</t>
+          <t>6,52; 6,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,53; 9,32</t>
+          <t>8,55; 9,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,44; 8,64</t>
+          <t>7,38; 8,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,09; 5,62</t>
+          <t>5,11; 5,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,87; 6,21</t>
+          <t>5,86; 6,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,86; 8,44</t>
+          <t>7,8; 8,41</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,89; 7,89</t>
+          <t>6,84; 7,78</t>
         </is>
       </c>
     </row>
